--- a/docs/pruebas/registro_defectos.xlsx
+++ b/docs/pruebas/registro_defectos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Odeth\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Corina\Desktop\ing\Joyería\docs\pruebas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{174BBC55-96B2-4A0B-AF87-1130E2EA975C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50BF28F-B2E1-4026-8DC2-2CBDDCA80C65}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F889B60-8F29-43C8-824A-42611A3341F6}"/>
+    <workbookView xWindow="696" yWindow="696" windowWidth="4104" windowHeight="9696" xr2:uid="{3F889B60-8F29-43C8-824A-42611A3341F6}"/>
   </bookViews>
   <sheets>
     <sheet name=" registro_defectos" sheetId="1" r:id="rId1"/>
@@ -23,12 +23,6 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -98,9 +92,6 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>Backend</t>
-  </si>
-  <si>
     <t>DF-03</t>
   </si>
   <si>
@@ -140,9 +131,6 @@
     <t>No se muestra mensaje de error al ingresar credenciales incorrectas</t>
   </si>
   <si>
-    <t>Frontend</t>
-  </si>
-  <si>
     <t>DF-06</t>
   </si>
   <si>
@@ -219,13 +207,19 @@
   </si>
   <si>
     <t>Conflicto al actualizar pedidos simultáneamente</t>
+  </si>
+  <si>
+    <t>Corina</t>
+  </si>
+  <si>
+    <t>Odeth</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,7 +240,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -256,6 +250,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1155CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -287,12 +293,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -630,12 +642,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E35DE417-B151-4364-910A-97C56FF46311}">
   <dimension ref="B2:H14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
-    <col min="5" max="5" width="18.21875" customWidth="1"/>
+    <col min="4" max="4" width="15.296875" customWidth="1"/>
+    <col min="5" max="5" width="18.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" ht="31.2">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -658,7 +671,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" ht="62.4">
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
@@ -674,14 +687,14 @@
       <c r="F3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8" ht="62.4">
       <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
@@ -697,200 +710,200 @@
       <c r="F4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="46.8">
+      <c r="B5" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="2:8" ht="93.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="62.4">
+      <c r="B6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" ht="109.2" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>24</v>
+      <c r="G6" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" ht="109.2" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="62.4">
       <c r="B7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>12</v>
       </c>
       <c r="H7" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="46.8">
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" spans="2:8" ht="93.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>12</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" ht="78" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="46.8">
       <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" ht="78" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="46.8">
       <c r="B10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" ht="62.4" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="31.2">
       <c r="B11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="3" t="s">
         <v>12</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" ht="62.4" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="31.2">
       <c r="B12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" ht="78" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="46.8">
       <c r="B13" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>8</v>
@@ -899,39 +912,39 @@
         <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="46.8">
+      <c r="B14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" ht="78" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
